--- a/xxx.xlsx
+++ b/xxx.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R10"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -463,49 +463,49 @@
         <v>I</v>
       </c>
       <c r="C2" t="str">
-        <v>66a15de6a4a14d000a51b08a</v>
+        <v>66a94b08da23cb001069719c</v>
       </c>
       <c r="D2" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="E2" t="str">
-        <v>MAAD</v>
+        <v>MACG002</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>2467</v>
+        <v>900</v>
       </c>
       <c r="H2" t="str">
-        <v>DA46195845</v>
+        <v>DA46195860</v>
       </c>
       <c r="I2" t="str">
-        <v>20240724201338368</v>
+        <v>20240730202713993</v>
       </c>
       <c r="K2" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="L2" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="M2" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="N2" t="str">
-        <v>台灣407台中市西屯區惠文二街40-1號</v>
+        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>cutejacquelline@gmail.com</v>
+        <v>twjasmine@hotmail.com</v>
       </c>
       <c r="Q2" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="R2" t="str">
-        <v>7280451964</v>
+        <v>7280625085</v>
       </c>
     </row>
     <row r="3">
@@ -516,49 +516,49 @@
         <v>I</v>
       </c>
       <c r="C3" t="str">
-        <v>66a15de6a4a14d000a51b08a</v>
+        <v>66a94b08da23cb001069719c</v>
       </c>
       <c r="D3" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="E3" t="str">
-        <v>MAUM101</v>
+        <v>MAJQ</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1567</v>
+        <v>1050</v>
       </c>
       <c r="H3" t="str">
-        <v>DA46195845</v>
+        <v>DA46195860</v>
       </c>
       <c r="I3" t="str">
-        <v>20240724201338368</v>
+        <v>20240730202713993</v>
       </c>
       <c r="K3" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="L3" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="M3" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="N3" t="str">
-        <v>台灣407台中市西屯區惠文二街40-1號</v>
+        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>cutejacquelline@gmail.com</v>
+        <v>twjasmine@hotmail.com</v>
       </c>
       <c r="Q3" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="R3" t="str">
-        <v>7280451964</v>
+        <v>7280625085</v>
       </c>
     </row>
     <row r="4">
@@ -569,49 +569,49 @@
         <v>I</v>
       </c>
       <c r="C4" t="str">
-        <v>66a15de6a4a14d000a51b08a</v>
+        <v>66a94b08da23cb001069719c</v>
       </c>
       <c r="D4" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="E4" t="str">
-        <v>MAKO004</v>
+        <v>ADD-L</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>806</v>
+        <v>80</v>
       </c>
       <c r="H4" t="str">
-        <v>DA46195845</v>
+        <v>DA46195860</v>
       </c>
       <c r="I4" t="str">
-        <v>20240724201338368</v>
+        <v>20240730202713993</v>
       </c>
       <c r="K4" t="str">
-        <v>張蔡昀潔</v>
+        <v>游小姐</v>
       </c>
       <c r="L4" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="M4" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="N4" t="str">
-        <v>台灣407台中市西屯區惠文二街40-1號</v>
+        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
       </c>
       <c r="O4" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>cutejacquelline@gmail.com</v>
+        <v>twjasmine@hotmail.com</v>
       </c>
       <c r="Q4" t="str">
-        <v>0937769926</v>
+        <v>0963061168</v>
       </c>
       <c r="R4" t="str">
-        <v>7280451964</v>
+        <v>7280625085</v>
       </c>
     </row>
     <row r="5">
@@ -622,49 +622,49 @@
         <v>I</v>
       </c>
       <c r="C5" t="str">
-        <v>66a15de6a4a14d000a51b08a</v>
+        <v>66a9c34e1b2a970010104774</v>
       </c>
       <c r="D5" t="str">
-        <v>張蔡昀潔</v>
+        <v>宋育維</v>
       </c>
       <c r="E5" t="str">
-        <v>ADMO24G2</v>
+        <v>MADC005</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>815</v>
       </c>
       <c r="H5" t="str">
-        <v>DA46195845</v>
+        <v>DA46195861</v>
       </c>
       <c r="I5" t="str">
-        <v>20240724201338368</v>
+        <v>20240731052517621</v>
       </c>
       <c r="K5" t="str">
-        <v>張蔡昀潔</v>
+        <v>宋育維</v>
       </c>
       <c r="L5" t="str">
-        <v>0937769926</v>
+        <v>0919612322</v>
       </c>
       <c r="M5" t="str">
-        <v>0937769926</v>
+        <v>0919612322</v>
       </c>
       <c r="N5" t="str">
-        <v>台灣407台中市西屯區惠文二街40-1號</v>
+        <v>台灣325桃園市龍潭區中興路45號</v>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>cutejacquelline@gmail.com</v>
+        <v>h14996015@gmail.com</v>
       </c>
       <c r="Q5" t="str">
-        <v>0937769926</v>
+        <v>0919612322</v>
       </c>
       <c r="R5" t="str">
-        <v>7280451964</v>
+        <v>7280642084</v>
       </c>
     </row>
     <row r="6">
@@ -675,49 +675,49 @@
         <v>I</v>
       </c>
       <c r="C6" t="str">
-        <v>66a1a9df5a4afc000e191e9a</v>
+        <v>66a9c34e1b2a970010104774</v>
       </c>
       <c r="D6" t="str">
-        <v>許恩綺</v>
+        <v>宋育維</v>
       </c>
       <c r="E6" t="str">
-        <v>MAQQ002</v>
+        <v>MADC001</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>815</v>
       </c>
       <c r="H6" t="str">
-        <v>DA46195846</v>
+        <v>DA46195861</v>
       </c>
       <c r="I6" t="str">
-        <v>20240725013157101</v>
+        <v>20240731052517621</v>
       </c>
       <c r="K6" t="str">
-        <v>許恩綺</v>
+        <v>宋育維</v>
       </c>
       <c r="L6" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="M6" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="N6" t="str">
-        <v>台灣621嘉義縣民雄鄉中樂路108-14號</v>
+        <v>台灣325桃園市龍潭區中興路45號</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>eee20161225@gmail.com</v>
+        <v>h14996015@gmail.com</v>
       </c>
       <c r="Q6" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="R6" t="str">
-        <v>7280451975</v>
+        <v>7280642084</v>
       </c>
     </row>
     <row r="7">
@@ -728,49 +728,49 @@
         <v>I</v>
       </c>
       <c r="C7" t="str">
-        <v>66a1a9df5a4afc000e191e9a</v>
+        <v>66a9c34e1b2a970010104774</v>
       </c>
       <c r="D7" t="str">
-        <v>許恩綺</v>
+        <v>宋育維</v>
       </c>
       <c r="E7" t="str">
-        <v>ADD-L</v>
+        <v>MAHB001</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>80</v>
+        <v>615</v>
       </c>
       <c r="H7" t="str">
-        <v>DA46195846</v>
+        <v>DA46195861</v>
       </c>
       <c r="I7" t="str">
-        <v>20240725013157101</v>
+        <v>20240731052517621</v>
       </c>
       <c r="K7" t="str">
-        <v>許恩綺</v>
+        <v>宋育維</v>
       </c>
       <c r="L7" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="M7" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="N7" t="str">
-        <v>台灣621嘉義縣民雄鄉中樂路108-14號</v>
+        <v>台灣325桃園市龍潭區中興路45號</v>
       </c>
       <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>eee20161225@gmail.com</v>
+        <v>h14996015@gmail.com</v>
       </c>
       <c r="Q7" t="str">
-        <v>0979169598</v>
+        <v>0919612322</v>
       </c>
       <c r="R7" t="str">
-        <v>7280451975</v>
+        <v>7280642084</v>
       </c>
     </row>
     <row r="8">
@@ -781,54 +781,160 @@
         <v>I</v>
       </c>
       <c r="C8" t="str">
-        <v>63b54ac8d9bce6000c253ed7</v>
+        <v>66a9c34e1b2a970010104774</v>
       </c>
       <c r="D8" t="str">
-        <v>rosephoenix</v>
+        <v>宋育維</v>
       </c>
       <c r="E8" t="str">
-        <v>MAAD</v>
+        <v>MAHB002</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>2500</v>
+        <v>615</v>
       </c>
       <c r="H8" t="str">
-        <v>DA46195847</v>
+        <v>DA46195861</v>
       </c>
       <c r="I8" t="str">
-        <v>20240725035255787</v>
+        <v>20240731052517621</v>
       </c>
       <c r="K8" t="str">
-        <v>黃馥蓉</v>
+        <v>宋育維</v>
       </c>
       <c r="L8" t="str">
-        <v>0918884484</v>
+        <v>0919612322</v>
       </c>
       <c r="M8" t="str">
-        <v>0918884484</v>
+        <v>0919612322</v>
       </c>
       <c r="N8" t="str">
-        <v>台灣500彰化縣彰化市旭光路251巷2號</v>
+        <v>台灣325桃園市龍潭區中興路45號</v>
       </c>
       <c r="O8" t="str">
         <v/>
       </c>
       <c r="P8" t="str">
-        <v>jungphoenix@gmail.com</v>
+        <v>h14996015@gmail.com</v>
       </c>
       <c r="Q8" t="str">
-        <v>0918884484</v>
+        <v>0919612322</v>
       </c>
       <c r="R8" t="str">
-        <v>7280451986</v>
+        <v>7280642084</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FG0003</v>
+      </c>
+      <c r="B9" t="str">
+        <v>I</v>
+      </c>
+      <c r="C9" t="str">
+        <v>66a9f6b870d91800135af2b4</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Eugenia Kuo</v>
+      </c>
+      <c r="E9" t="str">
+        <v>MAFT001</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1600</v>
+      </c>
+      <c r="H9" t="str">
+        <v>DA46195862</v>
+      </c>
+      <c r="I9" t="str">
+        <v>20240731084448140</v>
+      </c>
+      <c r="K9" t="str">
+        <v>郭采晴</v>
+      </c>
+      <c r="L9" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="M9" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="N9" t="str">
+        <v>台灣111台北市士林區延平北路五段70號3樓</v>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v>a0987821911@gmail.com</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="R9" t="str">
+        <v>7280651372</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>FG0003</v>
+      </c>
+      <c r="B10" t="str">
+        <v>I</v>
+      </c>
+      <c r="C10" t="str">
+        <v>66a9f6b870d91800135af2b4</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Eugenia Kuo</v>
+      </c>
+      <c r="E10" t="str">
+        <v>FABP014</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>750</v>
+      </c>
+      <c r="H10" t="str">
+        <v>DA46195862</v>
+      </c>
+      <c r="I10" t="str">
+        <v>20240731084448140</v>
+      </c>
+      <c r="K10" t="str">
+        <v>郭采晴</v>
+      </c>
+      <c r="L10" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="M10" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="N10" t="str">
+        <v>台灣111台北市士林區延平北路五段70號3樓</v>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v>a0987821911@gmail.com</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>0987821911</v>
+      </c>
+      <c r="R10" t="str">
+        <v>7280651372</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xxx.xlsx
+++ b/xxx.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R7"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -463,49 +463,49 @@
         <v>I</v>
       </c>
       <c r="C2" t="str">
-        <v>66a94b08da23cb001069719c</v>
+        <v>67b9a80cd65287000b4a63b9</v>
       </c>
       <c r="D2" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="E2" t="str">
-        <v>MACG002</v>
+        <v>MAFT002</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2">
-        <v>900</v>
+        <v>1617</v>
       </c>
       <c r="H2" t="str">
-        <v>DA46195860</v>
+        <v>JX21263125</v>
       </c>
       <c r="I2" t="str">
-        <v>20240730202713993</v>
+        <v>20250223043725077</v>
       </c>
       <c r="K2" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="L2" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="M2" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="N2" t="str">
-        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
+        <v>台灣542南投縣草屯鎮加老路281巷11號</v>
       </c>
       <c r="O2" t="str">
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>twjasmine@hotmail.com</v>
+        <v>lucky21443@gmail.com</v>
       </c>
       <c r="Q2" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="R2" t="str">
-        <v>7280625085</v>
+        <v>7211691233</v>
       </c>
     </row>
     <row r="3">
@@ -516,49 +516,49 @@
         <v>I</v>
       </c>
       <c r="C3" t="str">
-        <v>66a94b08da23cb001069719c</v>
+        <v>67b9a80cd65287000b4a63b9</v>
       </c>
       <c r="D3" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="E3" t="str">
-        <v>MAJQ</v>
+        <v>MAIM001</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1050</v>
+        <v>907</v>
       </c>
       <c r="H3" t="str">
-        <v>DA46195860</v>
+        <v>JX21263125</v>
       </c>
       <c r="I3" t="str">
-        <v>20240730202713993</v>
+        <v>20250223043725077</v>
       </c>
       <c r="K3" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="L3" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="M3" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="N3" t="str">
-        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
+        <v>台灣542南投縣草屯鎮加老路281巷11號</v>
       </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
-        <v>twjasmine@hotmail.com</v>
+        <v>lucky21443@gmail.com</v>
       </c>
       <c r="Q3" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="R3" t="str">
-        <v>7280625085</v>
+        <v>7211691233</v>
       </c>
     </row>
     <row r="4">
@@ -569,49 +569,49 @@
         <v>I</v>
       </c>
       <c r="C4" t="str">
-        <v>66a94b08da23cb001069719c</v>
+        <v>67b9a80cd65287000b4a63b9</v>
       </c>
       <c r="D4" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="E4" t="str">
-        <v>ADD-L</v>
+        <v>MAQM001</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>1166</v>
       </c>
       <c r="H4" t="str">
-        <v>DA46195860</v>
+        <v>JX21263125</v>
       </c>
       <c r="I4" t="str">
-        <v>20240730202713993</v>
+        <v>20250223043725077</v>
       </c>
       <c r="K4" t="str">
-        <v>游小姐</v>
+        <v>高鈺舒</v>
       </c>
       <c r="L4" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="M4" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="N4" t="str">
-        <v>台灣406台中市北屯區建和路一段436號2A3室</v>
+        <v>台灣542南投縣草屯鎮加老路281巷11號</v>
       </c>
       <c r="O4" t="str">
         <v/>
       </c>
       <c r="P4" t="str">
-        <v>twjasmine@hotmail.com</v>
+        <v>lucky21443@gmail.com</v>
       </c>
       <c r="Q4" t="str">
-        <v>0963061168</v>
+        <v>0972788822</v>
       </c>
       <c r="R4" t="str">
-        <v>7280625085</v>
+        <v>7211691233</v>
       </c>
     </row>
     <row r="5">
@@ -622,49 +622,49 @@
         <v>I</v>
       </c>
       <c r="C5" t="str">
-        <v>66a9c34e1b2a970010104774</v>
+        <v>6240261eb5340a000f84ce40</v>
       </c>
       <c r="D5" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="E5" t="str">
-        <v>MADC005</v>
+        <v>MATB101</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="G5">
-        <v>815</v>
+        <v>867</v>
       </c>
       <c r="H5" t="str">
-        <v>DA46195861</v>
+        <v>JX21263126</v>
       </c>
       <c r="I5" t="str">
-        <v>20240731052517621</v>
+        <v>20250223045808658</v>
       </c>
       <c r="K5" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="L5" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="M5" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="N5" t="str">
-        <v>台灣325桃園市龍潭區中興路45號</v>
+        <v>台灣335桃園市大溪區自強街4巷1號</v>
       </c>
       <c r="O5" t="str">
         <v/>
       </c>
       <c r="P5" t="str">
-        <v>h14996015@gmail.com</v>
+        <v>galaxy.zz@msa.hinet.net</v>
       </c>
       <c r="Q5" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="R5" t="str">
-        <v>7280642084</v>
+        <v>7211691266</v>
       </c>
     </row>
     <row r="6">
@@ -675,49 +675,49 @@
         <v>I</v>
       </c>
       <c r="C6" t="str">
-        <v>66a9c34e1b2a970010104774</v>
+        <v>6240261eb5340a000f84ce40</v>
       </c>
       <c r="D6" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="E6" t="str">
-        <v>MADC001</v>
+        <v>MATB102</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>815</v>
+        <v>867</v>
       </c>
       <c r="H6" t="str">
-        <v>DA46195861</v>
+        <v>JX21263126</v>
       </c>
       <c r="I6" t="str">
-        <v>20240731052517621</v>
+        <v>20250223045808658</v>
       </c>
       <c r="K6" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="L6" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="M6" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="N6" t="str">
-        <v>台灣325桃園市龍潭區中興路45號</v>
+        <v>台灣335桃園市大溪區自強街4巷1號</v>
       </c>
       <c r="O6" t="str">
         <v/>
       </c>
       <c r="P6" t="str">
-        <v>h14996015@gmail.com</v>
+        <v>galaxy.zz@msa.hinet.net</v>
       </c>
       <c r="Q6" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="R6" t="str">
-        <v>7280642084</v>
+        <v>7211691266</v>
       </c>
     </row>
     <row r="7">
@@ -728,213 +728,54 @@
         <v>I</v>
       </c>
       <c r="C7" t="str">
-        <v>66a9c34e1b2a970010104774</v>
+        <v>6240261eb5340a000f84ce40</v>
       </c>
       <c r="D7" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="E7" t="str">
-        <v>MAHB001</v>
+        <v>MAOG037</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H7" t="str">
-        <v>DA46195861</v>
+        <v>JX21263126</v>
       </c>
       <c r="I7" t="str">
-        <v>20240731052517621</v>
+        <v>20250223045808658</v>
       </c>
       <c r="K7" t="str">
-        <v>宋育維</v>
+        <v>李雅萍</v>
       </c>
       <c r="L7" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="M7" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="N7" t="str">
-        <v>台灣325桃園市龍潭區中興路45號</v>
+        <v>台灣335桃園市大溪區自強街4巷1號</v>
       </c>
       <c r="O7" t="str">
         <v/>
       </c>
       <c r="P7" t="str">
-        <v>h14996015@gmail.com</v>
+        <v>galaxy.zz@msa.hinet.net</v>
       </c>
       <c r="Q7" t="str">
-        <v>0919612322</v>
+        <v>0918673386</v>
       </c>
       <c r="R7" t="str">
-        <v>7280642084</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>FG0003</v>
-      </c>
-      <c r="B8" t="str">
-        <v>I</v>
-      </c>
-      <c r="C8" t="str">
-        <v>66a9c34e1b2a970010104774</v>
-      </c>
-      <c r="D8" t="str">
-        <v>宋育維</v>
-      </c>
-      <c r="E8" t="str">
-        <v>MAHB002</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>615</v>
-      </c>
-      <c r="H8" t="str">
-        <v>DA46195861</v>
-      </c>
-      <c r="I8" t="str">
-        <v>20240731052517621</v>
-      </c>
-      <c r="K8" t="str">
-        <v>宋育維</v>
-      </c>
-      <c r="L8" t="str">
-        <v>0919612322</v>
-      </c>
-      <c r="M8" t="str">
-        <v>0919612322</v>
-      </c>
-      <c r="N8" t="str">
-        <v>台灣325桃園市龍潭區中興路45號</v>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>h14996015@gmail.com</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>0919612322</v>
-      </c>
-      <c r="R8" t="str">
-        <v>7280642084</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>FG0003</v>
-      </c>
-      <c r="B9" t="str">
-        <v>I</v>
-      </c>
-      <c r="C9" t="str">
-        <v>66a9f6b870d91800135af2b4</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Eugenia Kuo</v>
-      </c>
-      <c r="E9" t="str">
-        <v>MAFT001</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1600</v>
-      </c>
-      <c r="H9" t="str">
-        <v>DA46195862</v>
-      </c>
-      <c r="I9" t="str">
-        <v>20240731084448140</v>
-      </c>
-      <c r="K9" t="str">
-        <v>郭采晴</v>
-      </c>
-      <c r="L9" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="M9" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="N9" t="str">
-        <v>台灣111台北市士林區延平北路五段70號3樓</v>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>a0987821911@gmail.com</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="R9" t="str">
-        <v>7280651372</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>FG0003</v>
-      </c>
-      <c r="B10" t="str">
-        <v>I</v>
-      </c>
-      <c r="C10" t="str">
-        <v>66a9f6b870d91800135af2b4</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Eugenia Kuo</v>
-      </c>
-      <c r="E10" t="str">
-        <v>FABP014</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>750</v>
-      </c>
-      <c r="H10" t="str">
-        <v>DA46195862</v>
-      </c>
-      <c r="I10" t="str">
-        <v>20240731084448140</v>
-      </c>
-      <c r="K10" t="str">
-        <v>郭采晴</v>
-      </c>
-      <c r="L10" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="M10" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="N10" t="str">
-        <v>台灣111台北市士林區延平北路五段70號3樓</v>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>a0987821911@gmail.com</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>0987821911</v>
-      </c>
-      <c r="R10" t="str">
-        <v>7280651372</v>
+        <v>7211691266</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R7"/>
   </ignoredErrors>
 </worksheet>
 </file>